--- a/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
@@ -659,7 +659,6 @@
           <t>True</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -689,7 +688,6 @@
           <t>NEXTEND</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>3</t>
@@ -707,7 +705,6 @@
           <t>SIMDATA</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>False</t>
@@ -725,7 +722,6 @@
           <t>SCIDATA</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>True</t>
@@ -809,7 +805,6 @@
           <t>CREATOR</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Pandora MOC</t>
@@ -827,7 +822,6 @@
           <t>CRSOFTV</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>v3.06</t>
@@ -845,7 +839,6 @@
           <t>COMPTYPE</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>0</t>
@@ -863,7 +856,6 @@
           <t>TRANSID</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>0</t>
@@ -881,7 +873,6 @@
           <t>TARG_ID</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>G1299384497902599936</t>
@@ -899,7 +890,6 @@
           <t>FILENAME</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>2026-07-12__02-42-32.525_VisImg_G1299384497902599936_d1280x1280x0010_b1_e000200000us.sp</t>
@@ -917,7 +907,6 @@
           <t>BINSIZE</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>1</t>
@@ -935,7 +924,6 @@
           <t>BITDEPTH</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>16</t>
@@ -953,7 +941,6 @@
           <t>BITSPIX</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>16</t>
@@ -971,7 +958,6 @@
           <t>ROISTRTX</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>384</t>
@@ -989,7 +975,6 @@
           <t>ROISTRTY</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>384</t>
@@ -1007,7 +992,6 @@
           <t>ROISTRTZ</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>0</t>
@@ -1025,7 +1009,6 @@
           <t>ROISIZEX</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>1280</t>
@@ -1043,7 +1026,6 @@
           <t>ROISIZEY</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>1280</t>
@@ -1061,7 +1043,6 @@
           <t>ROISIZEZ</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>10</t>
@@ -1079,7 +1060,6 @@
           <t>RICEX</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>3</t>
@@ -1097,7 +1077,6 @@
           <t>RICEY</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>11</t>
@@ -1115,7 +1094,6 @@
           <t>CORSTIME</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>837139385</t>
@@ -1133,7 +1111,6 @@
           <t>FINETIME</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>525000000</t>
@@ -1151,7 +1128,6 @@
           <t>CORRMODE</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>0</t>
@@ -1169,7 +1145,6 @@
           <t>EXPTIME</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>200000</t>
@@ -1187,7 +1162,6 @@
           <t>FRMSCLCT</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>10</t>
@@ -1205,7 +1179,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>5X9p5W8n5W8n5W8n</t>
@@ -1223,7 +1196,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>0</t>
@@ -1241,13 +1213,11 @@
           <t>FIXED</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1255,13 +1225,11 @@
           <t>PFSOFTV</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>0.6.0</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1269,13 +1237,11 @@
           <t>PRSOFTV</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>2.9.1</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1283,13 +1249,11 @@
           <t>PFCLASS</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>VISDAFFILevel2HDUList</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1297,7 +1261,6 @@
           <t>PFTIME</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>2026-09-09T19:46:14.050</t>
@@ -1315,9 +1278,6 @@
           <t>COMMENT</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1325,13 +1285,11 @@
           <t>COMMENT</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>Applied bias.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1441,13 +1399,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1455,13 +1411,11 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1469,13 +1423,11 @@
           <t>NAXIS3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1483,7 +1435,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>0</t>
@@ -1501,7 +1452,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
@@ -1541,7 +1491,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>dKgIdIZ9dIfGdIZ9</t>
@@ -1559,7 +1508,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>1747188824</t>
@@ -1577,26 +1525,14 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>COUNTS</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1705,7 +1641,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>50</t>
@@ -1723,7 +1658,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>10</t>
@@ -1741,7 +1675,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1759,7 +1692,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -1809,7 +1741,6 @@
           <t>ExposureStartTime_us</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1827,7 +1758,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1845,7 +1775,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1863,7 +1792,6 @@
           <t>Temperature</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1881,7 +1809,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1899,7 +1826,6 @@
           <t>26</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1929,7 +1855,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>lJ9qoI6nlI6nlI6n</t>
@@ -1947,7 +1872,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>490153783</t>
@@ -1970,7 +1894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2067,13 +1991,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2081,7 +2003,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2099,7 +2020,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -2117,7 +2037,6 @@
           <t>FRAME</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>JD</t>
@@ -2154,34 +2073,49 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>TIMEPIXR</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1deA4Zc71bcA1Zc5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-09T15:46:15</t>
+          <t>TIME is the middle of each exposure</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1deA4Zc71bcA1Zc5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-09-09T15:46:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>2634768335</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>data unit checksum updated 2026-09-09T15:46:15</t>
         </is>
@@ -2295,13 +2229,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2309,7 +2241,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2327,7 +2258,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -2345,7 +2275,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>second</t>
@@ -2385,7 +2314,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>aALad0IVa7IZa7IZ</t>
@@ -2403,7 +2331,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>2111832060</t>
@@ -2523,7 +2450,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>1280</t>
@@ -2541,7 +2467,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>1280</t>
@@ -2559,7 +2484,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -2577,7 +2501,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -2605,7 +2528,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2623,7 +2545,6 @@
           <t>32768</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2653,7 +2574,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>ZhGVfe9SZeGSfe9S</t>
@@ -2671,7 +2591,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>1113539193</t>

--- a/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
@@ -1970,7 +1970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2184,6 +2184,28 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>data unit checksum updated 2026-09-09T15:46:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TIMESYS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Time scale</t>
         </is>
       </c>
     </row>
